--- a/datasets/production-like-corpus/corpus/procurement/PROC-003_采购审批权限矩阵.xlsx
+++ b/datasets/production-like-corpus/corpus/procurement/PROC-003_采购审批权限矩阵.xlsx
@@ -512,7 +512,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -525,7 +525,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：PROC-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
+          <t>文档编号：NT-PROC-MAT-2026-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>PROC-001：≤5万元采购仅部门负责人审批</t>
+          <t>≤5万元采购仅部门负责人审批</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>PROC-002：5~20万元增加VP审批</t>
+          <t>5~20万元增加VP审批</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>PROC-003：20~100万元增加CFO审批</t>
+          <t>20~100万元增加CFO审批</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>PROC-004：&gt;100万元增加CEO审批</t>
+          <t>&gt;100万元增加CEO审批</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -682,7 +682,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：PROC-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
+          <t>文档编号：NT-PROC-MAT-2026-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>PROC-005：85万元软件采购需负责人+VP+CFO</t>
+          <t>85万元软件采购需负责人+VP+CFO</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：PROC-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
+          <t>文档编号：NT-PROC-MAT-2026-003    版本：V2.1    归口部门：PROCUREMENT    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>采购审批、合同签署权限、供应商准入、付款审批和单一来源例外分别留痕</t>
+          <t>合同金额权限与采购审批不是同一个流程；采购审批、合同签署权限、供应商准入、付款审批和单一来源例外分别留痕</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
